--- a/poker/resources/sample/PlayerLevelPack.xlsx
+++ b/poker/resources/sample/PlayerLevelPack.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevelPack" sheetId="1" r:id="rId1"/>
@@ -67,7 +72,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>等级</t>
+    <t>娱乐城等级</t>
   </si>
   <si>
     <t>等级奖励</t>
@@ -1246,7 +1251,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
@@ -1266,7 +1271,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
@@ -1286,7 +1291,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
@@ -1306,7 +1311,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>19</v>
@@ -1326,7 +1331,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -1346,7 +1351,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="1">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
@@ -1366,7 +1371,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>22</v>
@@ -1386,7 +1391,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>24</v>
@@ -1406,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>26</v>
@@ -1426,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -1446,7 +1451,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>30</v>
@@ -1466,7 +1471,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>31</v>
@@ -1486,7 +1491,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>31</v>
@@ -1506,7 +1511,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>33</v>
@@ -1526,7 +1531,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="1">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>33</v>
@@ -1546,7 +1551,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="1">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>35</v>
@@ -1566,7 +1571,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="1">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>35</v>
@@ -1586,7 +1591,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="1">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>37</v>
@@ -1606,7 +1611,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="1">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>37</v>
@@ -1626,7 +1631,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="1">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>37</v>

--- a/poker/resources/sample/PlayerLevelPack.xlsx
+++ b/poker/resources/sample/PlayerLevelPack.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -114,76 +114,103 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_1485000</t>
+    <t>1990000_1500000|1980000_500|1960000_20000|1024013_2</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
   </si>
   <si>
-    <t>1990000_2686000</t>
+    <t>1990000_1800000|1980000_1000|1960000_50000|1024014_2</t>
+  </si>
+  <si>
+    <t>1990000_2000000|1980000_1500|1960000_80000|1024013_5</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
   </si>
   <si>
-    <t>1990000_2627000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_3528000|1022502_2</t>
+    <t>1990000_2627000|1980000_2000|1022502_5|1024014_5</t>
+  </si>
+  <si>
+    <t>1990000_3528000|1022502_2|1022502_10|1024013_10</t>
   </si>
   <si>
     <t>1_googl299|2_ios299</t>
   </si>
   <si>
-    <t>1990000_5180000|1022502_2</t>
+    <t>1990000_3528000|1022502_2|1022502_20|1024014_10</t>
+  </si>
+  <si>
+    <t>1990000_5180000|1022502_2|1022502_30|1024013_10</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
   </si>
   <si>
-    <t>1990000_5242000|1022502_5</t>
+    <t>1990000_5242000|1022502_5|1022502_40|1024014_10</t>
   </si>
   <si>
     <t>1_google599|2_ios599</t>
   </si>
   <si>
-    <t>1990000_5841000|1022502_5|1010301_1</t>
+    <t>1990000_5841000|1022502_5|1010301_1|1022502_40</t>
   </si>
   <si>
     <t>1_google799|2_ios799</t>
   </si>
   <si>
-    <t>1990000_5839000|1022502_5|1010301_2</t>
+    <t>1990000_5839000|1022502_5|1010301_2|1022502_40</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
   </si>
   <si>
-    <t>1990000_5685000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_7785000|1022502_10|1010302_2</t>
+    <t>1990000_5685000|1022502_10|1010302_2|1022502_40</t>
+  </si>
+  <si>
+    <t>1990000_7785000|1022502_10|1010302_2|1022502_40</t>
   </si>
   <si>
     <t>1_google1499|2_ios1499</t>
   </si>
   <si>
-    <t>1990000_8686000|1022502_10|1010302_2</t>
+    <t>1990000_7785000|1022502_10|1010302_2|1024013_10|1024014_10</t>
+  </si>
+  <si>
+    <t>1990000_8686000|1022502_10|1010302_2|1024013_12|1024014_12</t>
   </si>
   <si>
     <t>1_google1999|2_ios1999</t>
   </si>
   <si>
-    <t>1990000_8366000|1022502_20|1010303_2</t>
+    <t>1990000_8686000|1022502_10|1010302_2|1024013_14|1024014_14</t>
+  </si>
+  <si>
+    <t>1990000_8366000|1022502_20|1010303_2|1024013_16|1024014_16</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
   </si>
   <si>
-    <t>1990000_12867000|1022502_20|1010303_2</t>
+    <t>1990000_8366000|1022502_20|1010303_2|1024013_18|1024014_18</t>
+  </si>
+  <si>
+    <t>1990000_12867000|1022502_20|1010303_2|1024013_20|1024014_20</t>
   </si>
   <si>
     <t>1_google4999|2_ios4999</t>
+  </si>
+  <si>
+    <t>1990000_12867000|1022502_20|1010303_2|1024013_25|1024014_25</t>
+  </si>
+  <si>
+    <t>1990000_12867000|1022502_20|1010303_2|1024013_30|1024014_30</t>
+  </si>
+  <si>
+    <t>1990000_12867000|1022502_20|1010303_2|1024013_40|1024014_40</t>
+  </si>
+  <si>
+    <t>1990000_12867000|1022502_20|1010303_2|1024013_50|1024014_50</t>
   </si>
 </sst>
 </file>
@@ -1170,12 +1197,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="72.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="25.75" style="1" customWidth="1"/>
@@ -1251,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
@@ -1271,10 +1298,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1">
         <v>120</v>
@@ -1291,10 +1318,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
@@ -1303,7 +1330,7 @@
         <v>1.99</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1311,10 +1338,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1">
         <v>120</v>
@@ -1323,7 +1350,7 @@
         <v>1.99</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1331,19 +1358,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1">
         <v>120</v>
       </c>
       <c r="E9" s="1">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1351,10 +1378,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1">
         <v>120</v>
@@ -1363,7 +1390,7 @@
         <v>2.99</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1371,19 +1398,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
       </c>
       <c r="E11" s="1">
-        <v>4.99</v>
+        <v>2.99</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1391,19 +1418,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="1">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
       </c>
       <c r="E12" s="1">
-        <v>5.99</v>
+        <v>2.99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1411,19 +1438,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" s="1">
         <v>120</v>
       </c>
       <c r="E13" s="1">
-        <v>7.99</v>
+        <v>4.99</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1431,19 +1458,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
       </c>
       <c r="E14" s="1">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1451,19 +1478,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1">
         <v>120</v>
       </c>
       <c r="E15" s="1">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1471,19 +1498,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="1">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1">
         <v>120</v>
       </c>
       <c r="E16" s="1">
-        <v>14.99</v>
+        <v>9.99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1491,19 +1518,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="1">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1">
         <v>120</v>
       </c>
       <c r="E17" s="1">
-        <v>14.99</v>
+        <v>9.99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1511,19 +1538,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="1">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D18" s="1">
         <v>120</v>
       </c>
       <c r="E18" s="1">
-        <v>19.99</v>
+        <v>9.99</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1531,10 +1558,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1">
         <v>120</v>
@@ -1543,7 +1570,7 @@
         <v>19.99</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1551,19 +1578,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="1">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1">
         <v>120</v>
       </c>
       <c r="E20" s="1">
-        <v>24.99</v>
+        <v>19.99</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1571,19 +1598,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="1">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D21" s="1">
         <v>120</v>
       </c>
       <c r="E21" s="1">
-        <v>24.99</v>
+        <v>19.99</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1591,19 +1618,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="1">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D22" s="1">
         <v>120</v>
       </c>
       <c r="E22" s="1">
-        <v>49.99</v>
+        <v>19.99</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1611,19 +1638,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="1">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D23" s="1">
         <v>120</v>
       </c>
       <c r="E23" s="1">
-        <v>49.99</v>
+        <v>24.99</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1631,19 +1658,59 @@
         <v>20</v>
       </c>
       <c r="B24" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D24" s="1">
         <v>120</v>
       </c>
       <c r="E24" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1">
+        <v>58</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="1">
+        <v>120</v>
+      </c>
+      <c r="E25" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1">
+        <v>60</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="1">
+        <v>120</v>
+      </c>
+      <c r="E26" s="1">
         <v>49.99</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>38</v>
+      <c r="F26" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
